--- a/bakery_dairy_overrides.xlsx
+++ b/bakery_dairy_overrides.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B48"/>
+  <dimension ref="A1:B47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bagel Plain</t>
+          <t>Bagel plain</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BBQ Cheese &amp; Bacon Roll</t>
+          <t>BBQ cheese &amp; bacon roll</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cheese &amp; Bacon Roll</t>
+          <t>Cheese &amp; bacon roll</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Double Choc Muffin</t>
+          <t>Double choc muffin</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ham &amp; Cheese Croissant</t>
+          <t>Ham &amp; cheese croissant</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Rye Bread</t>
+          <t>Rye bread</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Wholemeal Wrap</t>
+          <t>Wholemeal wrap</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Wholemeal Pizza Base</t>
+          <t>Wholemeal pizza base</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Wholemeal Roll</t>
+          <t>Wholemeal roll</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Soy Milk</t>
+          <t>Soy milk</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Reduced Fat Cheddar Cheese</t>
+          <t>Reduced fat cheddar cheese</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Fresh Napoli Sauce</t>
+          <t>Fresh napoli sauce</t>
         </is>
       </c>
     </row>
@@ -779,216 +779,204 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DEF11</t>
+          <t>DEF12</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Champagne Leg Ham</t>
+          <t>Coconut yoghurt</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DEF12</t>
+          <t>DEF13</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Coconut yoghurt</t>
+          <t>Salami</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DEF13</t>
+          <t>DEF14</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Salami</t>
+          <t>Roast Pastrami Sliced</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DEF14</t>
+          <t>DEF15</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Roast Pastrami Sliced</t>
+          <t>Chicken breast sliced</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DEF15</t>
+          <t>DEF16</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Chicken Breast Thinly Sliced</t>
+          <t>Fresh carbonara pasta sauce</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DEF16</t>
+          <t>DEF17</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fresh Carbonara Pasta Sauce</t>
+          <t>Middle Bacon</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DEF17</t>
+          <t>DEF18</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Middle Bacon</t>
+          <t>Silverside sliced</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DEF18</t>
+          <t>DEF19</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Silverside sliced</t>
+          <t>Chocolate chip yoghurt</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DEF19</t>
+          <t>DEF20</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Chocolate chip yoghurt</t>
+          <t>Maple Bacon</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DEF20</t>
+          <t>DEF21</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Maple Bacon</t>
+          <t>Chicken shredded</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DEF21</t>
+          <t>DEF22</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Chicken shredded</t>
+          <t>Kabana</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DEF22</t>
+          <t>DEF23</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Kabana</t>
+          <t>Prosciutto Sliced</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DEF23</t>
+          <t>DEF24</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Prosciutto Sliced</t>
+          <t>Turkey breast sliced</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DEF24</t>
+          <t>DEF25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Turkey breast sliced</t>
+          <t>High protein chocolate pudding</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DEF25</t>
+          <t>DEF26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>High Protein Chocolate Pudding</t>
+          <t>Sliced Pancetta</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DEF26</t>
+          <t>DEF27</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Sliced Pancetta</t>
+          <t>Smiley Fritz</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DEF27</t>
+          <t>DEF28</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Smiley Fritz</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>DEF28</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Short Cut Bacon</t>
+          <t>Short cut bacon</t>
         </is>
       </c>
     </row>
